--- a/notebooks/Outputs Excel/Horarios_Docentes_Colegio_MMDD.xlsx
+++ b/notebooks/Outputs Excel/Horarios_Docentes_Colegio_MMDD.xlsx
@@ -1852,7 +1852,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DISTRIBUCIÓN DE HORAS POR ASIGNATURAS – AÑO ACADÉMICO 2026.</t>
+          <t>DISTRIBUCIÓN DE HORAS POR ASIGNATURAS – AÑO ACADÉMICO 2027.</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8218,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -8836,7 +8836,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -10269,7 +10269,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -11008,7 +11008,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -11747,7 +11747,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -12533,7 +12533,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -13152,7 +13152,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -13731,7 +13731,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -14306,7 +14306,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -14937,7 +14937,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -15551,7 +15551,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -16186,7 +16186,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -16965,7 +16965,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -17496,7 +17496,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -18111,7 +18111,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -18758,7 +18758,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -19572,7 +19572,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -20283,7 +20283,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -21089,7 +21089,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -21608,7 +21608,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -22219,7 +22219,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -22750,7 +22750,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -23343,7 +23343,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -23922,7 +23922,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -24483,7 +24483,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -25064,7 +25064,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -25645,7 +25645,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -26226,7 +26226,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -26807,7 +26807,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -27388,7 +27388,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -27967,7 +27967,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -28554,7 +28554,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -29065,7 +29065,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -29488,7 +29488,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -30065,7 +30065,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
@@ -30528,7 +30528,7 @@
     </row>
     <row r="6">
       <c r="B6" s="14" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7" ht="5.25" customHeight="1"/>
